--- a/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête. Il dit : papa, je peux l'avoir ? Il va demander. Papa, c'est l'adulte. Papa écoute. Papa dit : aujourd'hui, on achète le pain. Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
+          <t>Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête. Papa, je peux l'avoir ? Il va demander. Papa, c'est l'adulte. Papa écoute. Aujourd'hui, on achète le pain. Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête.
+narrateur|Papa, je peux l'avoir ? Il va demander. Papa, c'est l'adulte. Papa écoute.
+papa|Aujourd'hui, on achète le pain.
+narrateur|Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Amine veut un gâteau. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amine a demandé à l'adulte. Papa a répondu. L'argent est resté avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin, Amine sent le pain. Il tient la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Amine veut un gâteau. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Amine a demandé à l'adulte. Papa a répondu. L'argent est resté avec papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Sur le chemin, Amine sent le pain. Il tient la main de papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amine demande pour un achat</t>
+          <t>La pêche de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut une pêche au stand. Elle tend la main. Papa attend. Elle demande. La pêche est à elle.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête. Papa, je peux l'avoir ? Il va demander. Papa, c'est l'adulte. Papa écoute. Aujourd'hui, on achète le pain. Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
+          <t>Les pêches brillent dans la caisse. Le bois est chaud. Ça sent le sucre. Une abeille tourne tout près. Papa tient le cabas. Mila marche à côté. Le sol est un peu poudreux. Une feuille colle à sa chaussure. Une caisse de prunes est plus loin. Les prunes sont sombres, toutes lisses. Un parasol fait une ombre ronde. Mila entre dans l'ombre. Tu as vu les fruits ? Oui. Ils brillent. Ça sent bon, tu vois ? Oui, papa. Un grain de sable colle au bois. En ce moment, Mila s'arrête. Elle voit une pêche. La pêche est ronde. Elle est jaune et rose. Je la veux. Mila tend la main. Ses doigts touchent le duvet. Papa ne bouge pas. Mila. Tu demandes ? La main s'arrête. La pêche reste dans la caisse. Oh. On achète si tu demandes. Je peux demander. Tu me dis s'il te plaît ? Oui, papa. L'abeille s'éloigne. Une autre pêche roule un peu. Le duvet de la pêche brille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête. Il dit : papa, je peux l'avoir ? Il va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt;. Papa, c'est l'adulte. Papa écoute. Papa dit : aujourd'hui, on achète le pain. Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les pêches brillent dans la caisse. Le bois est chaud. Ça sent le sucre. Une abeille tourne tout près. Papa tient le cabas. Mila marche à côté. Le sol est un peu poudreux. Une feuille colle à sa chaussure. Une caisse de prunes est plus loin. Les prunes sont sombres, toutes lisses. Un parasol fait une ombre ronde. Mila entre dans l'ombre. Tu as vu les fruits ? Oui. Ils brillent. Ça sent bon, tu vois ? Oui, papa. Un grain de sable colle au bois. En ce moment, Mila s'arrête. Elle voit une pêche. La pêche est ronde. Elle est jaune et rose. Je la veux. Mila tend la main. Ses doigts touchent le duvet. Papa ne bouge pas. Mila. Tu demandes ? La main s'arrête. La pêche reste dans la caisse. Oh. On achète si tu demandes. Je peux demander. Tu me dis s'il te plaît ? Oui, papa. L'abeille s'éloigne. Une autre pêche roule un peu. Le duvet de la pêche brille.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Amine entre à la boulangerie. Papa est là. Ça sent le pain chaud. Amine voit un petit gâteau. Il a envie. L'argent est dans la poche de papa. Papa range l'argent. Amine s'arrête.
-narrateur|Papa, je peux l'avoir ? Il va demander. Papa, c'est l'adulte. Papa écoute.
-papa|Aujourd'hui, on achète le pain.
-narrateur|Le gâteau attendra. Amine sent un petit pincement. Puis il respire. Il a demandé. Papa prend sa main. Ils prennent le pain. L'argent reste avec l'adulte. Pour un achat, on va demander. On demande à papa ou maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les pêches brillent dans la caisse.
+narrateur|Le bois est chaud.
+narrateur|Ça sent le sucre.
+narrateur|Une abeille tourne tout près.
+narrateur|Papa tient le cabas.
+narrateur|Mila marche à côté.
+narrateur|Le sol est un peu poudreux.
+narrateur|Une feuille colle à sa chaussure.
+narrateur|Une caisse de prunes est plus loin.
+narrateur|Les prunes sont sombres, toutes lisses.
+narrateur|Un parasol fait une ombre ronde.
+narrateur|Mila entre dans l'ombre.
+papa|Tu as vu les fruits ?
+enfant-f|Oui.
+enfant-f|Ils brillent.
+papa|Ça sent bon, tu vois ?
+enfant-f|Oui, papa.
+narrateur|Un grain de sable colle au bois.
+narrateur|En ce moment, Mila s'arrête.
+narrateur|Elle voit une pêche.
+narrateur|La pêche est ronde.
+narrateur|Elle est jaune et rose.
+enfant-f|Je la veux.
+narrateur|Mila tend la main.
+narrateur|Ses doigts touchent le duvet.
+narrateur|Papa ne bouge pas.
+papa|Mila.
+papa|Tu demandes ?
+narrateur|La main s'arrête.
+narrateur|La pêche reste dans la caisse.
+enfant-f|Oh.
+papa|On achète si tu demandes.
+enfant-f|Je peux demander.
+papa|Tu me dis s'il te plaît ?
+enfant-f|Oui, papa.
+narrateur|L'abeille s'éloigne.
+narrateur|Une autre pêche roule un peu.
+narrateur|Le duvet de la pêche brille.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amine veut un gâteau. Que fait-il ?</t>
+          <t>Mila veut la pêche. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine veut un gâteau. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila veut la pêche. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1408,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | il demande | à papa | demander à papa</t>
+          <t>demander | elle demande | à papa | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il parle à papa. Que fait Amine ?</t>
+          <t>Elle demande à papa. Que fait Mila ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1472,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1544,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amine veut un gâteau. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Mila veut la pêche.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amine a demandé à l'adulte. Papa a répondu. L'argent est resté avec papa.</t>
+          <t>Papa, s'il te plaît. Je peux avoir la pêche ? Oui. Merci, Mila. Tu as demandé. Papa pose l'argent. On lui tend la pêche. Mila la prend. Elle est douce, un peu chaude. Elle est à moi. Oui. Parce que tu as demandé. Tu la tiens bien ? Oui, papa. Le cabas reste ouvert. Mila garde la pêche. Elle la tourne dans sa paume. Le rose est plus chaud que le jaune. Elle est mûre. Elle est douce. Un peu de duvet reste au doigt.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amine a demandé à l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;. Papa a répondu. L'argent est resté avec papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa, s'il te plaît. Je peux avoir la pêche ? Oui. Merci, Mila. Tu as demandé. Papa pose l'argent. On lui tend la pêche. Mila la prend. Elle est douce, un peu chaude. Elle est à moi. Oui. Parce que tu as demandé. Tu la tiens bien ? Oui, papa. Le cabas reste ouvert. Mila garde la pêche. Elle la tourne dans sa paume. Le rose est plus chaud que le jaune. Elle est mûre. Elle est douce. Un peu de duvet reste au doigt.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1588,14 +1633,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1716,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amine a demandé à l'adulte. Papa a répondu. L'argent est resté avec papa.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|Papa, s'il te plaît.
+enfant-f|Je peux avoir la pêche ?
+papa|Oui.
+papa|Merci, Mila.
+papa|Tu as demandé.
+narrateur|Papa pose l'argent.
+narrateur|On lui tend la pêche.
+narrateur|Mila la prend.
+narrateur|Elle est douce, un peu chaude.
+enfant-f|Elle est à moi.
+papa|Oui.
+papa|Parce que tu as demandé.
+papa|Tu la tiens bien ?
+enfant-f|Oui, papa.
+narrateur|Le cabas reste ouvert.
+narrateur|Mila garde la pêche.
+narrateur|Elle la tourne dans sa paume.
+narrateur|Le rose est plus chaud que le jaune.
+papa|Elle est mûre.
+enfant-f|Elle est douce.
+narrateur|Un peu de duvet reste au doigt.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, Amine sent le pain. Il tient la main de papa.</t>
+          <t>Ils quittent le stand. Le bois craque un peu. Mila marche avec la pêche. Le duvet chatouille sa paume. On rentre ? Oui. Avec la pêche. La rue sent encore le sucre. Une feuille tourne. Tu as demandé. Bravo. Mila serre la pêche. Elle la sent encore. Ça sent le soleil. Papa prend sa main libre. Je tiens la pêche. Oui. Ils passent près d'une flaque.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sur le chemin, Amine sent le pain. Il tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils quittent le stand. Le bois craque un peu. Mila marche avec la pêche. Le duvet chatouille sa paume. On rentre ? Oui. Avec la pêche. La rue sent encore le sucre. Une feuille tourne. Tu as demandé. Bravo. Mila serre la pêche. Elle la sent encore. Ça sent le soleil. Papa prend sa main libre. Je tiens la pêche. Oui. Ils passent près d'une flaque.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1760,14 +1824,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1903,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, Amine sent le pain. Il tient la main de papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils quittent le stand.
+narrateur|Le bois craque un peu.
+narrateur|Mila marche avec la pêche.
+narrateur|Le duvet chatouille sa paume.
+papa|On rentre ?
+enfant-f|Oui.
+enfant-f|Avec la pêche.
+narrateur|La rue sent encore le sucre.
+narrateur|Une feuille tourne.
+papa|Tu as demandé.
+papa|Bravo.
+narrateur|Mila serre la pêche.
+narrateur|Elle la sent encore.
+narrateur|Ça sent le soleil.
+narrateur|Papa prend sa main libre.
+enfant-f|Je tiens la pêche.
+papa|Oui.
+narrateur|Ils passent près d'une flaque.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>À la maison, Mila s'assoit. Elle croque la pêche. Le jus est sucré. Il brille sur son menton. Elle est bonne. Oui. Tu l'as dans les mains. Mila tient le noyau. Il est lisse et chaud. Elle le pose près du cabas. Il reste. Oui. Le cœur de la pêche. Mila essuie son menton. Le jus de pêche brille sur son menton.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la maison, Mila s'assoit. Elle croque la pêche. Le jus est sucré. Il brille sur son menton. Elle est bonne. Oui. Tu l'as dans les mains. Mila tient le noyau. Il est lisse et chaud. Elle le pose près du cabas. Il reste. Oui. Le cœur de la pêche. Mila essuie son menton. Le jus de pêche brille sur son menton.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1928,14 +2008,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2087,23 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|À la maison, Mila s'assoit.
+narrateur|Elle croque la pêche.
+narrateur|Le jus est sucré.
+narrateur|Il brille sur son menton.
+enfant-f|Elle est bonne.
+papa|Oui.
+papa|Tu l'as dans les mains.
+narrateur|Mila tient le noyau.
+narrateur|Il est lisse et chaud.
+narrateur|Elle le pose près du cabas.
+enfant-f|Il reste.
+papa|Oui.
+papa|Le cœur de la pêche.
+narrateur|Mila essuie son menton.
+narrateur|Le jus de pêche brille sur son menton.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boulangerie</t>
+          <t>stand de fruits, caisses en bois, soleil</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amine, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
